--- a/email_dashboard.xlsx
+++ b/email_dashboard.xlsx
@@ -777,7 +777,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 05 April 2026, 11:09  |  Threads: 10  |  Powered by: sumy · KeyBERT · VADER · spaCy</t>
+          <t>Generated: 05 April 2026, 11:27  |  Threads: 10  |  Powered by: sumy · KeyBERT · VADER · spaCy</t>
         </is>
       </c>
     </row>
